--- a/splashlipidomix_list.xlsx
+++ b/splashlipidomix_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Desktop/Doctorado_CEU/HUMAN_QCs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A36C604-6488-4142-BE36-E5ABF4874F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78867CC8-5B71-F043-B56B-5130EF578098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1760" yWindow="760" windowWidth="27640" windowHeight="16780" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
+    <workbookView xWindow="1760" yWindow="760" windowWidth="21360" windowHeight="16780" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
   <si>
     <t>Endogenos</t>
   </si>
@@ -108,6 +108,42 @@
   </si>
   <si>
     <t>SM1</t>
+  </si>
+  <si>
+    <t>CAR</t>
+  </si>
+  <si>
+    <t>dLysoPC</t>
+  </si>
+  <si>
+    <t>dLysoPE</t>
+  </si>
+  <si>
+    <t>LPC</t>
+  </si>
+  <si>
+    <t>dPG</t>
+  </si>
+  <si>
+    <t>dSM</t>
+  </si>
+  <si>
+    <t>dPC</t>
+  </si>
+  <si>
+    <t>dPE</t>
+  </si>
+  <si>
+    <t>dDG</t>
+  </si>
+  <si>
+    <t>dTG</t>
+  </si>
+  <si>
+    <t>dCE</t>
+  </si>
+  <si>
+    <t>short_name</t>
   </si>
 </sst>
 </file>
@@ -547,6 +583,9 @@
       <c r="E1" t="s">
         <v>20</v>
       </c>
+      <c r="F1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
@@ -565,6 +604,9 @@
         <f>D2*60</f>
         <v>48</v>
       </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
@@ -585,6 +627,9 @@
         <f t="shared" ref="E3:E18" si="0">D3*60</f>
         <v>153.6</v>
       </c>
+      <c r="F3" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
     </row>
@@ -605,6 +650,9 @@
         <f t="shared" si="0"/>
         <v>164.57999999999998</v>
       </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
@@ -625,6 +673,9 @@
         <f t="shared" si="0"/>
         <v>170.88</v>
       </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
     </row>
@@ -645,6 +696,9 @@
         <f t="shared" si="0"/>
         <v>254.4</v>
       </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
     </row>
@@ -665,6 +719,9 @@
         <f t="shared" si="0"/>
         <v>371.40000000000003</v>
       </c>
+      <c r="F7" t="s">
+        <v>6</v>
+      </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
     </row>
@@ -685,6 +742,9 @@
         <f t="shared" si="0"/>
         <v>387.6</v>
       </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
     </row>
@@ -705,6 +765,9 @@
         <f t="shared" si="0"/>
         <v>436.26</v>
       </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
     </row>
@@ -725,6 +788,9 @@
         <f t="shared" si="0"/>
         <v>465.59999999999997</v>
       </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
     </row>
@@ -745,6 +811,9 @@
         <f t="shared" si="0"/>
         <v>490.26</v>
       </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
     </row>
@@ -765,6 +834,9 @@
         <f t="shared" si="0"/>
         <v>510.18</v>
       </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
     </row>
@@ -785,6 +857,9 @@
         <f t="shared" si="0"/>
         <v>685.8</v>
       </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
@@ -805,6 +880,9 @@
         <f t="shared" si="0"/>
         <v>700.8</v>
       </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
     </row>
@@ -825,6 +903,9 @@
         <f t="shared" si="0"/>
         <v>735</v>
       </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
     </row>
@@ -845,6 +926,9 @@
         <f t="shared" si="0"/>
         <v>838.2</v>
       </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
     </row>
@@ -865,6 +949,9 @@
         <f t="shared" si="0"/>
         <v>839.88</v>
       </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
     </row>
@@ -884,6 +971,9 @@
       <c r="E18">
         <f t="shared" si="0"/>
         <v>927.6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>34</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>

--- a/splashlipidomix_list.xlsx
+++ b/splashlipidomix_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Desktop/Doctorado_CEU/HUMAN_QCs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78867CC8-5B71-F043-B56B-5130EF578098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF8CB13-C17B-A245-874D-6D121508AE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1760" yWindow="760" windowWidth="21360" windowHeight="16780" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
   <si>
     <t>Endogenos</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>short_name</t>
+  </si>
+  <si>
+    <t>TG(52:0)</t>
+  </si>
+  <si>
+    <t>TG1</t>
   </si>
 </sst>
 </file>
@@ -561,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD69E1-DE54-004B-BA8F-573A6CD4FC04}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -978,6 +984,27 @@
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
     </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="8">
+        <v>880.83274340259902</v>
+      </c>
+      <c r="D19" s="9">
+        <v>16.05</v>
+      </c>
+      <c r="E19">
+        <f>D19*60</f>
+        <v>963</v>
+      </c>
+      <c r="F19" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
